--- a/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
+++ b/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
@@ -1,81 +1,148 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBDE666-177A-49A7-8211-4E6A8130F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
+    <sheet name="Présences" sheetId="1" r:id="rId1"/>
+    <sheet name="📖 Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:6c100576-061b-499f-ba1a-d7bb8f55165d</t>
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:61c8e0dd-28c7-4952-90c1-d32dc9216095</t>
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:2168818a-40b3-4f4c-b007-5323ceeb1185</t>
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:5771f77c-aed6-4eae-92b6-6147f3f339ff</t>
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:10045b96-6db6-437c-a80a-d5957db37ac2</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:5371930a-259d-4214-810a-cc7b39931d0d</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:b3c5a76d-4076-4574-aadb-8cc0b35f5966</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:c80afb8c-7e41-4ed0-b2a6-7214cd797ba1</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>student_id:a62cd3ee-b067-4266-a803-2e72fcb49154</t>
         </r>
       </text>
@@ -85,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>حموي فوج خاص  |  ANNEX  |  BAC  |  حموي عبد السلام</t>
   </si>
@@ -111,15 +178,15 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>كتاب
 ت 1</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>كتاب
 ت 2</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>كتاب
 ت 3</t>
   </si>
   <si>
@@ -181,51 +248,73 @@
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
+  </si>
+  <si>
+    <t>28/8/2026</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>18/9/2026</t>
+  </si>
+  <si>
+    <t>19/9/2026</t>
+  </si>
+  <si>
+    <t>25/9/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b/>
+      <sz val="9"/>
       <color rgb="FFC00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="666666"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="12">
@@ -313,14 +402,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -350,6 +433,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,37 +780,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+    </row>
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -729,584 +821,582 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="14">
+        <v>46121</v>
+      </c>
+      <c r="F4" s="14">
+        <v>46151</v>
+      </c>
+      <c r="G4" s="14">
+        <v>46335</v>
+      </c>
+      <c r="H4" s="14">
+        <v>46365</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="N4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>197</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0</v>
-      </c>
-      <c r="J5" s="10">
-        <v>0</v>
-      </c>
-      <c r="K5" s="10">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10">
-        <v>0</v>
-      </c>
-      <c r="M5" s="10">
-        <v>0</v>
-      </c>
-      <c r="N5" s="10">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0</v>
-      </c>
-      <c r="P5" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>428</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="12">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
-        <v>0</v>
-      </c>
-      <c r="I6" s="12">
-        <v>0</v>
-      </c>
-      <c r="J6" s="12">
-        <v>0</v>
-      </c>
-      <c r="K6" s="12">
-        <v>0</v>
-      </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12">
-        <v>0</v>
-      </c>
-      <c r="O6" s="11">
-        <v>0</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>429</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="10">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>430</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="12">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <v>0</v>
-      </c>
-      <c r="I8" s="12">
-        <v>0</v>
-      </c>
-      <c r="J8" s="12">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12">
-        <v>0</v>
-      </c>
-      <c r="L8" s="12">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12">
-        <v>0</v>
-      </c>
-      <c r="O8" s="11">
-        <v>0</v>
-      </c>
-      <c r="P8" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>431</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <v>0</v>
-      </c>
-      <c r="K9" s="10">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>432</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="12">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
-        <v>0</v>
-      </c>
-      <c r="I10" s="12">
-        <v>0</v>
-      </c>
-      <c r="J10" s="12">
-        <v>0</v>
-      </c>
-      <c r="K10" s="12">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12">
-        <v>0</v>
-      </c>
-      <c r="N10" s="12">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>433</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>434</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="11">
-        <v>0</v>
-      </c>
-      <c r="P12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>435</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="10">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0</v>
-      </c>
-      <c r="N13" s="10">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11">
-        <v>0</v>
-      </c>
-      <c r="P13" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11">
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
+        <v>0</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1316,24 +1406,24 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1409,6 +1499,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
+++ b/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
@@ -1,147 +1,146 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBDE666-177A-49A7-8211-4E6A8130F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Présences" sheetId="1" r:id="rId1"/>
-    <sheet name="📖 Instructions" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B5" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:6c100576-061b-499f-ba1a-d7bb8f55165d</t>
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B6" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:61c8e0dd-28c7-4952-90c1-d32dc9216095</t>
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:2168818a-40b3-4f4c-b007-5323ceeb1185</t>
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:5771f77c-aed6-4eae-92b6-6147f3f339ff</t>
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:10045b96-6db6-437c-a80a-d5957db37ac2</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:5371930a-259d-4214-810a-cc7b39931d0d</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:b3c5a76d-4076-4574-aadb-8cc0b35f5966</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:c80afb8c-7e41-4ed0-b2a6-7214cd797ba1</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:a62cd3ee-b067-4266-a803-2e72fcb49154</t>
         </r>
@@ -152,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>حموي فوج خاص  |  ANNEX  |  BAC  |  حموي عبد السلام</t>
   </si>
@@ -178,15 +177,42 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>كتاب
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>05/09/2026</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>12/09/2026</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب
 ت 1</t>
   </si>
   <si>
-    <t>كتاب
+    <t xml:space="preserve">كتاب
 ت 2</t>
   </si>
   <si>
-    <t>كتاب
+    <t xml:space="preserve">كتاب
 ت 3</t>
   </si>
   <si>
@@ -248,62 +274,47 @@
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
-  </si>
-  <si>
-    <t>28/8/2026</t>
-  </si>
-  <si>
-    <t>29/08/2026</t>
-  </si>
-  <si>
-    <t>18/9/2026</t>
-  </si>
-  <si>
-    <t>19/9/2026</t>
-  </si>
-  <si>
-    <t>25/9/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color rgb="FFC00000"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFC00000"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF666666"/>
       <sz val="9"/>
-      <color rgb="FF666666"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -402,8 +413,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -411,7 +428,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -433,15 +450,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,37 +788,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-    </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="27.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -821,582 +829,582 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="14">
-        <v>46121</v>
-      </c>
-      <c r="F4" s="14">
-        <v>46151</v>
-      </c>
-      <c r="G4" s="14">
-        <v>46335</v>
-      </c>
-      <c r="H4" s="14">
-        <v>46365</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="O4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
         <v>197</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8">
-        <v>1</v>
-      </c>
-      <c r="J5" s="8">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="B5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
         <v>428</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8">
-        <v>1</v>
-      </c>
-      <c r="K6" s="8">
-        <v>1</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="B6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10">
+        <v>1</v>
+      </c>
+      <c r="L6" s="12">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
         <v>429</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8">
-        <v>1</v>
-      </c>
-      <c r="J7" s="8">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8">
-        <v>1</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="B7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
         <v>430</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="8">
-        <v>1</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="B8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10">
+        <v>1</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12">
+        <v>0</v>
+      </c>
+      <c r="N8" s="12">
+        <v>0</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
         <v>431</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="8">
-        <v>1</v>
-      </c>
-      <c r="K9" s="8">
-        <v>1</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="B9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
         <v>432</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
-        <v>1</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="8">
-        <v>1</v>
-      </c>
-      <c r="K10" s="8">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="10">
-        <v>0</v>
-      </c>
-      <c r="N10" s="10">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9">
-        <v>0</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="B10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="10">
+        <v>1</v>
+      </c>
+      <c r="J10" s="10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0</v>
+      </c>
+      <c r="N10" s="12">
+        <v>0</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
         <v>433</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8">
-        <v>1</v>
-      </c>
-      <c r="K11" s="8">
-        <v>1</v>
-      </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="B11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10">
+        <v>1</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10">
+        <v>1</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
         <v>434</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8">
-        <v>1</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1</v>
-      </c>
-      <c r="I12" s="8">
-        <v>1</v>
-      </c>
-      <c r="J12" s="8">
-        <v>1</v>
-      </c>
-      <c r="K12" s="8">
-        <v>1</v>
-      </c>
-      <c r="L12" s="10">
-        <v>0</v>
-      </c>
-      <c r="M12" s="10">
-        <v>0</v>
-      </c>
-      <c r="N12" s="10">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="B12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
+        <v>1</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12">
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
         <v>435</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="8">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8">
-        <v>1</v>
-      </c>
-      <c r="I13" s="8">
-        <v>1</v>
-      </c>
-      <c r="J13" s="8">
-        <v>1</v>
-      </c>
-      <c r="K13" s="8">
-        <v>1</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
+      <c r="B13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1</v>
+      </c>
+      <c r="H13" s="10">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10">
+        <v>1</v>
+      </c>
+      <c r="K13" s="10">
+        <v>1</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1406,25 +1414,25 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
+    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1434,12 +1442,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -1449,27 +1457,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -1479,12 +1487,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -1494,11 +1502,11 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
+++ b/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6c100576-061b-499f-ba1a-d7bb8f55165d</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:61c8e0dd-28c7-4952-90c1-d32dc9216095</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:2168818a-40b3-4f4c-b007-5323ceeb1185</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:5771f77c-aed6-4eae-92b6-6147f3f339ff</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:10045b96-6db6-437c-a80a-d5957db37ac2</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:5371930a-259d-4214-810a-cc7b39931d0d</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b3c5a76d-4076-4574-aadb-8cc0b35f5966</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c80afb8c-7e41-4ed0-b2a6-7214cd797ba1</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a62cd3ee-b067-4266-a803-2e72fcb49154</t>
         </r>
       </text>
@@ -151,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
   <si>
     <t>حموي فوج خاص  |  ANNEX  |  BAC  |  حموي عبد السلام</t>
   </si>
@@ -165,6 +99,9 @@
     <t>has_books=true</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -204,7 +141,17 @@
     <t>25/09/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب 1
+ت 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب 2
 ت 1</t>
   </si>
   <si>
@@ -216,7 +163,7 @@
 ت 3</t>
   </si>
   <si>
-    <t>عويدي سرين هديل</t>
+    <t>عويدي سيرين هديل</t>
   </si>
   <si>
     <t>نعيجة جيهان</t>
@@ -270,7 +217,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -292,40 +242,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="12">
@@ -428,7 +371,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -789,15 +732,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,8 +760,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-    </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -828,10 +772,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -871,99 +818,107 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="O4" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>197</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="10">
         <v>0</v>
@@ -983,40 +938,43 @@
       <c r="Q5" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>428</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>1</v>
-      </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="I6" s="10">
-        <v>1</v>
-      </c>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12">
+        <v>0</v>
       </c>
       <c r="L6" s="12">
         <v>0</v>
@@ -1036,40 +994,43 @@
       <c r="Q6" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>429</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="10">
         <v>0</v>
@@ -1089,40 +1050,43 @@
       <c r="Q7" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>430</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10">
-        <v>1</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10">
-        <v>1</v>
-      </c>
-      <c r="J8" s="10">
-        <v>1</v>
-      </c>
-      <c r="K8" s="10">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0</v>
       </c>
       <c r="L8" s="12">
         <v>0</v>
@@ -1142,40 +1106,43 @@
       <c r="Q8" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>431</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="10">
         <v>0</v>
@@ -1195,40 +1162,43 @@
       <c r="Q9" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>432</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="10">
-        <v>1</v>
-      </c>
-      <c r="J10" s="10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0</v>
+      </c>
+      <c r="K10" s="12">
+        <v>0</v>
       </c>
       <c r="L10" s="12">
         <v>0</v>
@@ -1248,40 +1218,43 @@
       <c r="Q10" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>433</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="10">
         <v>0</v>
@@ -1301,40 +1274,43 @@
       <c r="Q11" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>434</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="10">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10">
-        <v>1</v>
-      </c>
-      <c r="G12" s="10">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10">
-        <v>1</v>
-      </c>
-      <c r="I12" s="10">
-        <v>1</v>
-      </c>
-      <c r="J12" s="10">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0</v>
       </c>
       <c r="L12" s="12">
         <v>0</v>
@@ -1354,40 +1330,43 @@
       <c r="Q12" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>435</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="10">
         <v>0</v>
@@ -1405,16 +1384,19 @@
         <v>0</v>
       </c>
       <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1424,89 +1406,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
+++ b/data/attendance/ANNEX_حموي_فوج_خاص.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7983248C-F7B5-4C22-A0CC-8093334375A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
+    <sheet name="Présences" sheetId="1" r:id="rId1"/>
+    <sheet name="📖 Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>حموي فوج خاص  |  ANNEX  |  BAC  |  حموي عبد السلام</t>
   </si>
@@ -41,19 +45,19 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب 1
+    <t>كتاب 1
 ت 1</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب 2
+    <t>كتاب 2
 ت 1</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>كتاب
 ت 2</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>كتاب
 ت 3</t>
   </si>
   <si>
@@ -126,49 +130,56 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b/>
+      <sz val="9"/>
       <color rgb="FFC00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="666666"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -220,11 +231,6 @@
         <fgColor rgb="FFFFF4E8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F5FF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -255,12 +261,6 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -286,10 +286,16 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,38 +634,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+    </row>
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -673,673 +679,673 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="13">
+        <v>46262</v>
+      </c>
+      <c r="D4" s="13">
+        <v>46263</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46269</v>
+      </c>
+      <c r="F4" s="13">
+        <v>46270</v>
+      </c>
+      <c r="G4" s="13">
+        <v>46276</v>
+      </c>
+      <c r="H4" s="13">
+        <v>46277</v>
+      </c>
+      <c r="I4" s="13">
+        <v>46283</v>
+      </c>
+      <c r="J4" s="13">
+        <v>46284</v>
+      </c>
+      <c r="K4" s="13">
+        <v>46290</v>
+      </c>
+      <c r="L4" s="13">
+        <v>46297</v>
+      </c>
+      <c r="M4" s="13">
+        <v>46298</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>53</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0</v>
-      </c>
-      <c r="J5" s="10">
-        <v>0</v>
-      </c>
-      <c r="K5" s="10">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10">
-        <v>0</v>
-      </c>
-      <c r="M5" s="10">
-        <v>0</v>
-      </c>
-      <c r="N5" s="10">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11">
-        <v>0</v>
-      </c>
-      <c r="P5" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="11">
-        <v>0</v>
-      </c>
-      <c r="R5" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1</v>
+      </c>
+      <c r="L5" s="8">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>1</v>
+      </c>
+      <c r="P5" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>0</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>54</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="12">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
-        <v>0</v>
-      </c>
-      <c r="I6" s="12">
-        <v>0</v>
-      </c>
-      <c r="J6" s="12">
-        <v>0</v>
-      </c>
-      <c r="K6" s="12">
-        <v>0</v>
-      </c>
-      <c r="L6" s="12">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12">
-        <v>0</v>
-      </c>
-      <c r="O6" s="11">
-        <v>0</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>0</v>
-      </c>
-      <c r="R6" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1</v>
+      </c>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9">
+        <v>1</v>
+      </c>
+      <c r="P6" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>55</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="10">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11">
-        <v>0</v>
-      </c>
-      <c r="P7" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <v>1</v>
+      </c>
+      <c r="P7" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>56</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="12">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12">
-        <v>0</v>
-      </c>
-      <c r="G8" s="12">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <v>0</v>
-      </c>
-      <c r="I8" s="12">
-        <v>0</v>
-      </c>
-      <c r="J8" s="12">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12">
-        <v>0</v>
-      </c>
-      <c r="L8" s="12">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12">
-        <v>0</v>
-      </c>
-      <c r="O8" s="11">
-        <v>0</v>
-      </c>
-      <c r="P8" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="8">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>1</v>
+      </c>
+      <c r="P8" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>57</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <v>0</v>
-      </c>
-      <c r="K9" s="10">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1</v>
+      </c>
+      <c r="L9" s="8">
+        <v>1</v>
+      </c>
+      <c r="M9" s="8">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>1</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>58</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="12">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12">
-        <v>0</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
-        <v>0</v>
-      </c>
-      <c r="I10" s="12">
-        <v>0</v>
-      </c>
-      <c r="J10" s="12">
-        <v>0</v>
-      </c>
-      <c r="K10" s="12">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12">
-        <v>0</v>
-      </c>
-      <c r="N10" s="12">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0</v>
-      </c>
-      <c r="R10" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8">
+        <v>1</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>1</v>
+      </c>
+      <c r="P10" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>59</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="10">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>0</v>
-      </c>
-      <c r="R11" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1</v>
+      </c>
+      <c r="M11" s="8">
+        <v>1</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <v>1</v>
+      </c>
+      <c r="P11" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>60</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0</v>
-      </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
-      <c r="O12" s="11">
-        <v>0</v>
-      </c>
-      <c r="P12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>1</v>
+      </c>
+      <c r="P12" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>61</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="10">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0</v>
-      </c>
-      <c r="N13" s="10">
-        <v>0</v>
-      </c>
-      <c r="O13" s="11">
-        <v>0</v>
-      </c>
-      <c r="P13" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>0</v>
-      </c>
-      <c r="R13" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
+        <v>1</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>62</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
-        <v>0</v>
-      </c>
-      <c r="F14" s="12">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12">
-        <v>0</v>
-      </c>
-      <c r="J14" s="12">
-        <v>0</v>
-      </c>
-      <c r="K14" s="12">
-        <v>0</v>
-      </c>
-      <c r="L14" s="12">
-        <v>0</v>
-      </c>
-      <c r="M14" s="12">
-        <v>0</v>
-      </c>
-      <c r="N14" s="12">
-        <v>0</v>
-      </c>
-      <c r="O14" s="11">
-        <v>0</v>
-      </c>
-      <c r="P14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>0</v>
-      </c>
-      <c r="R14" s="11">
+      <c r="C14" s="8">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8">
+        <v>1</v>
+      </c>
+      <c r="M14" s="8">
+        <v>1</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
+        <v>1</v>
+      </c>
+      <c r="P14" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1349,23 +1355,23 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1446,6 +1452,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>